--- a/planilha_presenca.xlsx
+++ b/planilha_presenca.xlsx
@@ -478,7 +478,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>X</v>
       </c>
       <c r="G2" t="str">
         <v/>
